--- a/pdf2img/tabel/table_8.xlsx
+++ b/pdf2img/tabel/table_8.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,11 +447,20 @@
       <c r="J1" t="n">
         <v>9</v>
       </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPORAN</t>
+          <t>LUAPORAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,78 +480,118 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Per,31/Desember,2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>[Per,31/Desember</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dan'2024</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>{</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jutaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rupiah</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{</t>
+          <t>NO.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dalam</t>
+          <t>POS-POS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jutaan</t>
+          <t>31-Des-25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rupiah</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>)</t>
-        </is>
-      </c>
+          <t>31-Des-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NO.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>RASIO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KINERJA</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -551,83 +600,155 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31-Des-24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>|Kewajiban</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Penyediaan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(KPMM)</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RASIO</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KINERJA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>|Aset</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>produktif</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bermasalah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>produktif</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>bermasalah</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>terhadap</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>produktif</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>|Kewajiban</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Penyediaan</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>{(KPMM)</t>
-        </is>
-      </c>
+          <t>produktif</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,105 +758,134 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>produkiif</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>bermasalah</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>terhadap</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>produktif</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>bermasalah</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>produktif</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>bermasalah</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>terhadap</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>produktif</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>|Cadangan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kerugian</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Penurunan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Nilai</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{CKPN}</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>aset</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>keuangan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>terhadap</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>aset</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>produktif</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>produktif</t>
-        </is>
-      </c>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+          <t>6,</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -743,306 +893,420 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aset</t>
+          <t>7.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>produktif</t>
+          <t>|Return</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bermasalah</t>
+          <t>on</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>terhadap</t>
+          <t>Assef</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>(RCA)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>produktif</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cadangan</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kerugian</t>
+          <t>|Return</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Penurunan</t>
+          <t>on</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(CKPN}</t>
+          <t>(ROE}</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>kKeuangan</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>terhadap</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>produktif</t>
-        </is>
-      </c>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>9.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>|Net</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(ROA)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>(NIM)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>10.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>|Biaya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(ROE}</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Operasional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>terhadap</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pendapatan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Operasional</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{(BOPO}</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{CIR)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>12.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>|Loan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(NIM)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(LDR)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>84,01%</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>13.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>|Biaya</t>
+          <t>|</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Operasional</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>terhadap</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>Funding</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operasional</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>({BOPO}</t>
+          <t>(NSFR)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11.</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>NSFR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>secara</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Individu</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ratio</t>
+          <t>147,62%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{CIR)</t>
+          <t>145,19%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fo</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NSFR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>secara</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Konsolidasi</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>14.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>|Loan</t>
+          <t>|Nilai</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fo</t>
+          <t>Liquidity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,101 +1316,113 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(LDR)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>77,65%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
+          <t>{LCR}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LCR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>secara</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Individu</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>b.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>secara</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Funding</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>(NSFR)</t>
-        </is>
-      </c>
+          <t>Konsolidasi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>16.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Individu</t>
+          <t>|Nilai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>147,62%</t>
+          <t>Leverage</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>145,19%</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(LR}</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1156,17 +1432,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>secara</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Individu</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,29 +1463,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Konsolidasi</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>secara</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Konsalidasi</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>KEPATUHAN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{COMPLIANCE)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -1207,55 +1505,61 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>|Nilai</t>
+          <t>|a.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liquidity</t>
+          <t>Persentase</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Pelanggaran</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>{LCR}</t>
-        </is>
-      </c>
+          <t>BMPK</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>i.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Individu</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Pihak</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Terkait</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1263,26 +1567,40 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a.</t>
+          <t>ii.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>Pihak</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Terkait</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1292,30 +1610,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>Persentase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Konsolidasi</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Pelampauan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BMPK</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>i.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pihak</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Terkait</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1323,54 +1656,75 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>18.</t>
+          <t>ii.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>|Nilai</t>
+          <t>Pihak</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leverage</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>(LR}</t>
-        </is>
-      </c>
+          <t>Terkait</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Individu</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>|Giro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(GWM)</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1380,38 +1734,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>GWM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>utama</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>rupiah</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Konsolidasi</t>
-        </is>
-      </c>
+          <t>Harian</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1419,14 +1776,21 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rata-rata</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -1435,18 +1799,17 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KEPATUHAN</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>(COMPLIANCE)</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -1455,402 +1818,79 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>GWM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ja.</t>
+          <t>valuta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Persentase</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Pelanggaran</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>BMPK</t>
-        </is>
-      </c>
+          <t>asing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>i.</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pihak</t>
+          <t>|Posisi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>Devisa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(PDN)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>secara</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>keseluruhan</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ii,</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Pihak</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>b.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Persentase</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Pelampauan</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>BMPK</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>i.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Pihak</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ii,</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Pihak</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Giro</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Wajib</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>(GWM)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>GWM</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>utama</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>rupiah</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Harian</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Rata-rata</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>GWM</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>valuta</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>asing</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>|Posisi</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Devisa</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Neto</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(PDN}</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>secara</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>keseluruhan</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
